--- a/files/港岛-赤柱-50 Stanley Village Road.xlsx
+++ b/files/港岛-赤柱-50 Stanley Village Road.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2015-05-08</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -860,7 +860,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2015-04-28</t>
+          <t>2015-04-29</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2015-05-04</t>
+          <t>2015-05-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2015-05-13</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2017-11-21</t>
+          <t>2017-11-22</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2015-05-08</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2015-05-13</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2016-03-28</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1603,7 +1603,7 @@
         <is>
           <t>2号屋
 3233呎 (4+房)
-(15年-05月-07日)
+(15年-05月-08日)
 $1.49亿
 $45,939/呎</t>
         </is>
@@ -1612,7 +1612,7 @@
         <is>
           <t>3号屋
 3179呎 (4+房)
-(15年-04月-28日)
+(15年-04月-29日)
 $1.69亿
 $53,254/呎</t>
         </is>
@@ -1621,7 +1621,7 @@
         <is>
           <t>5号屋
 2760呎 (3房)
-(19年-04月-14日)
+(19年-04月-15日)
 $1.69亿
 $61,159/呎</t>
         </is>
@@ -1630,7 +1630,7 @@
         <is>
           <t>6号屋
 2725呎 (3房)
-(15年-05月-04日)
+(15年-05月-05日)
 $1.27亿
 $46,776/呎</t>
         </is>
@@ -1639,7 +1639,7 @@
         <is>
           <t>7号屋
 2725呎 (3房)
-(15年-05月-20日)
+(15年-05月-21日)
 $1.46亿
 $53,744/呎</t>
         </is>
@@ -1655,7 +1655,7 @@
         <is>
           <t>8号屋
 2895呎 (3房)
-(25年-05月-22日)
+(25年-05月-23日)
 $1.07亿
 $36,891/呎</t>
         </is>
@@ -1664,7 +1664,7 @@
         <is>
           <t>9号屋
 2725呎 (3房)
-(15年-05月-13日)
+(15年-05月-14日)
 $1.26亿
 $46,155/呎</t>
         </is>
@@ -1673,7 +1673,7 @@
         <is>
           <t>10号屋
 2725呎 (3房)
-(17年-11月-21日)
+(17年-11月-22日)
 $1.46亿
 $53,394/呎</t>
         </is>
@@ -1682,7 +1682,7 @@
         <is>
           <t>11号屋
 2725呎 (3房)
-(15年-05月-07日)
+(15年-05月-08日)
 $1.26亿
 $46,293/呎</t>
         </is>
@@ -1691,7 +1691,7 @@
         <is>
           <t>12号屋
 2713呎 (3房)
-(15年-05月-13日)
+(15年-05月-14日)
 $1.22亿
 $45,086/呎</t>
         </is>
@@ -1700,7 +1700,7 @@
         <is>
           <t>15号屋
 2751呎 (3房)
-(16年-03月-28日)
+(16年-03月-29日)
 $1.36亿
 $49,364/呎</t>
         </is>

--- a/files/港岛-赤柱-50 Stanley Village Road.xlsx
+++ b/files/港岛-赤柱-50 Stanley Village Road.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1266,7 +1275,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1285,7 +1294,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2725</v>
+        <v>2713</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1294,14 +1303,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-05-08</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>126148000</v>
+        <v>122317000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>46293</v>
+        <v>45086</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1309,10 +1318,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>126148000</v>
+        <v>122317000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>46293</v>
+        <v>45086</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1337,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1347,7 +1356,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2713</v>
+        <v>2751</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1356,14 +1365,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>122317000</v>
+        <v>135800000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>45086</v>
+        <v>49364</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1371,10 +1380,10 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>122317000</v>
+        <v>135800000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>45086</v>
+        <v>49364</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1382,68 +1391,6 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>15号屋</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2751</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2016-03-29</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>135800000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>49364</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>135800000</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>49364</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1518,7 +1465,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>12 套</t>
+          <t>11 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1533,7 +1480,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>11 套</t>
+          <t>10 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1680,15 +1627,6 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>11号屋
-2725呎 (3房)
-(15年-05月-08日)
-$1.26亿
-$46,293/呎</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
           <t>12号屋
 2713呎 (3房)
 (15年-05月-14日)
@@ -1696,7 +1634,7 @@
 $45,086/呎</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>15号屋
 2751呎 (3房)
@@ -1705,6 +1643,7 @@
 $49,364/呎</t>
         </is>
       </c>
+      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/港岛-赤柱-50 Stanley Village Road.xlsx
+++ b/files/港岛-赤柱-50 Stanley Village Road.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -238,9 +232,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1266,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1294,7 +1285,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2713</v>
+        <v>2725</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1303,14 +1294,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2015-05-08</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>122317000</v>
+        <v>126148000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>45086</v>
+        <v>46293</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1318,10 +1309,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>122317000</v>
+        <v>126148000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>45086</v>
+        <v>46293</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1337,60 +1328,122 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>12号屋</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>2713</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2015-05-14</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>122317000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>45086</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>122317000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>45086</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>15号屋</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>2751</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>2016-03-29</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>135800000</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>49364</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>135800000</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L14" s="5" t="n">
         <v>49364</v>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1465,22 +1518,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>12 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>11 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>10 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1627,6 +1680,15 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
+          <t>11号屋
+2725呎 (3房)
+(15年-05月-08日)
+$1.26亿
+$46,293/呎</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
           <t>12号屋
 2713呎 (3房)
 (15年-05月-14日)
@@ -1634,7 +1696,7 @@
 $45,086/呎</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>15号屋
 2751呎 (3房)
@@ -1643,7 +1705,6 @@
 $49,364/呎</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
